--- a/有父体1.0合并表/跟卖表.xlsx
+++ b/有父体1.0合并表/跟卖表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12315" windowHeight="9525"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="375">
   <si>
     <t>TemplateType=fptcustom</t>
   </si>
@@ -1152,18 +1152,6 @@
   </si>
   <si>
     <t>progressive_discount_value3</t>
-  </si>
-  <si>
-    <t>HM-HG-2P-CZS-902-1</t>
-  </si>
-  <si>
-    <t>B0CZDJ8RMW</t>
-  </si>
-  <si>
-    <t>ASIN</t>
-  </si>
-  <si>
-    <t>Update</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2302,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:GQ57"/>
+  <dimension ref="A1:GQ56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="24" width="9" hidden="1" customWidth="1"/>
@@ -3751,16 +3739,10 @@
     </row>
     <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="1:27">
       <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
-        <v>375</v>
-      </c>
+      <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>377</v>
-      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -3780,9 +3762,7 @@
       <c r="V4" s="7"/>
       <c r="W4" s="7"/>
       <c r="X4" s="6"/>
-      <c r="Y4" s="6" t="s">
-        <v>378</v>
-      </c>
+      <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
     </row>
@@ -4366,7 +4346,7 @@
       <c r="Z24" s="6"/>
       <c r="AA24" s="6"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="16" customHeight="1" spans="1:27">
+    <row r="25" spans="1:27">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -5294,35 +5274,6 @@
       <c r="Z56" s="6"/>
       <c r="AA56" s="6"/>
     </row>
-    <row r="57" spans="1:27">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="7"/>
-      <c r="O57" s="7"/>
-      <c r="P57" s="7"/>
-      <c r="Q57" s="7"/>
-      <c r="R57" s="7"/>
-      <c r="S57" s="7"/>
-      <c r="T57" s="7"/>
-      <c r="U57" s="7"/>
-      <c r="V57" s="7"/>
-      <c r="W57" s="7"/>
-      <c r="X57" s="6"/>
-      <c r="Y57" s="6"/>
-      <c r="Z57" s="6"/>
-      <c r="AA57" s="6"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
